--- a/naver-place-crawler/results_hair/관악_미용실.xlsx
+++ b/naver-place-crawler/results_hair/관악_미용실.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V140"/>
+  <dimension ref="A1:V233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12341,34 +12341,34 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>건물,구축물해체공사</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>철거천국 관악점</t>
+          <t>꼼리헤어</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>kang0825123@naver.com</t>
+          <t>didwjdwn87@naver.com</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0504-1360-1077</t>
+          <t>0507-1358-2884</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 승방길 27 제 A동 제B102호-2026</t>
+          <t>서울특별시 관악구 쑥고개로 64 1층 103호</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/yang.ssem</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -12399,17 +12399,17 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="Q129" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="R129" t="n">
-        <v>72</v>
+        <v>424</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -12418,12 +12418,12 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>2082818976</t>
+          <t>1974647123</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2082818976</t>
+          <t>https://m.place.naver.com/place/1974647123</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -12435,30 +12435,34 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>루이네</t>
+          <t>에이바헤어 신림역점</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>luinedesign@naver.com</t>
+          <t>avabbh-@naver.com</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0507-1484-2029</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 구암길 37 1층 루이네(반려견미용실)</t>
+          <t>서울특별시 관악구 남부순환로 1600 3층</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/louis_petsalon</t>
+          <t>https://blog.naver.com/avabbh-</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -12473,7 +12477,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -12489,17 +12493,17 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>23</v>
+        <v>30114</v>
       </c>
       <c r="Q130" t="n">
-        <v>2</v>
+        <v>2242</v>
       </c>
       <c r="R130" t="n">
-        <v>25</v>
+        <v>32356</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -12508,12 +12512,12 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>1801986146</t>
+          <t>1731887060</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1801986146</t>
+          <t>https://m.place.naver.com/place/1731887060</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -12525,34 +12529,30 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>힐링아로마 보그펫</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>vogue_pet@naver.com</t>
-        </is>
-      </c>
+          <t>오늘도원헤어</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0507-1330-2915</t>
+          <t>02-6012-7498</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 청림길 14 힐링아로마 보그펫</t>
+          <t>서울특별시 관악구 청림6길 19-1 1층</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vogue_pet</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -12583,17 +12583,17 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="Q131" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="R131" t="n">
-        <v>146</v>
+        <v>258</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -12602,12 +12602,12 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>1666008066</t>
+          <t>1629325934</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1666008066</t>
+          <t>https://m.place.naver.com/place/1629325934</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
@@ -12619,34 +12619,34 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>아우어썸머 바버샵</t>
+          <t>오월</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>durudgh118@naver.com</t>
+          <t>tmfvmspf52@naver.com</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0507-1489-2464</t>
+          <t>0507-1327-4276</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 관악로10길 31-20 라온아뜨 1층 아우어썸머 바버샵</t>
+          <t>서울특별시 관악구 남부순환로 1385 1층</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/k_ho0602/</t>
+          <t>https://blog.naver.com/tmfvmspf52</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -12677,17 +12677,17 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P132" t="n">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="Q132" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="R132" t="n">
-        <v>660</v>
+        <v>631</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -12696,12 +12696,12 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>1677236508</t>
+          <t>1498256544</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1677236508</t>
+          <t>https://m.place.naver.com/place/1498256544</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -12713,35 +12713,39 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>애리조나</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>메모리헤어</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>omoggy@naver.com</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0507-1362-9905</t>
+          <t>02-889-7787</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로200길 9 1층</t>
+          <t>서울특별시 관악구 관악로12길 16 길성아파트 1층</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barber_kenzo</t>
+          <t>http://cafe.naver.com/cyeos</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -12767,17 +12771,17 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P133" t="n">
-        <v>508</v>
+        <v>1146</v>
       </c>
       <c r="Q133" t="n">
-        <v>32</v>
+        <v>348</v>
       </c>
       <c r="R133" t="n">
-        <v>540</v>
+        <v>1494</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -12786,12 +12790,12 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>1074430929</t>
+          <t>37653649</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1074430929</t>
+          <t>https://m.place.naver.com/place/37653649</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
@@ -12803,39 +12807,39 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>인페르노바버샵</t>
+          <t>블랑코헤어</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>wnstjd7878@naver.com</t>
+          <t>sysysy0302@naver.com</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0507-1319-6246</t>
+          <t>0507-1334-0426</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 은천로 170 1층</t>
+          <t>서울특별시 관악구 남현길 3 2층</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wnstjd7878</t>
+          <t>http://www.instagram.com/blanco.hairsalon</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -12865,13 +12869,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>739</v>
+        <v>2293</v>
       </c>
       <c r="Q134" t="n">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="R134" t="n">
-        <v>789</v>
+        <v>2419</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -12880,12 +12884,12 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>1853395879</t>
+          <t>1519184232</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853395879</t>
+          <t>https://m.place.naver.com/place/1519184232</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
@@ -12897,34 +12901,34 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>지금은나의이발사</t>
+          <t>HAIR DK</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>mybaber@naver.com</t>
+          <t>polanroli@naver.com</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0505-300-8835</t>
+          <t>02-6013-1809</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 낙성대역길 39 1층</t>
+          <t>서울특별시 관악구 양녕로2길 26</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mybaber</t>
+          <t>https://blog.naver.com/polanroli</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -12962,10 +12966,10 @@
         <v>21</v>
       </c>
       <c r="Q135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R135" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -12974,12 +12978,12 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>1856833468</t>
+          <t>1166581995</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1856833468</t>
+          <t>https://m.place.naver.com/place/1166581995</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
@@ -12991,34 +12995,34 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>페니레인바버샵</t>
+          <t>리안헤어 신림점</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1024ty@naver.com</t>
+          <t>sj771218@naver.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>0507-1392-2465</t>
+          <t>0507-1407-8121</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 조원중앙로2길 121 1층 바버샵</t>
+          <t>서울특별시 관악구 신림로 344 에스케이허브그린 2층 213, 214, 215, 216호</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1024ty</t>
+          <t>https://blog.naver.com/sj771218</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -13053,13 +13057,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>116</v>
+        <v>8992</v>
       </c>
       <c r="Q136" t="n">
-        <v>2</v>
+        <v>1739</v>
       </c>
       <c r="R136" t="n">
-        <v>118</v>
+        <v>10731</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -13068,12 +13072,12 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>1833183810</t>
+          <t>31213050</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1833183810</t>
+          <t>https://m.place.naver.com/place/31213050</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
@@ -13085,34 +13089,34 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>쎄 비 바버샵</t>
+          <t>헤어비앙꼬 서울대입구역점</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>barberblxk@naver.com</t>
+          <t>bluesky8764@naver.com</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>0507-1306-4820</t>
+          <t>0507-1481-1115</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로214길 29 1층</t>
+          <t>서울특별시 관악구 남부순환로 1773 마에스트로캠퍼스 103호</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/c.est_b_barbershop.kr</t>
+          <t>https://www.instagram.com/hair_bianco?igsh=MTJlZTR0Y3g2ZnZwZw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -13147,13 +13151,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>496</v>
+        <v>904</v>
       </c>
       <c r="Q137" t="n">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="R137" t="n">
-        <v>575</v>
+        <v>946</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -13162,12 +13166,12 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>1438442640</t>
+          <t>1697463647</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438442640</t>
+          <t>https://m.place.naver.com/place/1697463647</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
@@ -13179,34 +13183,34 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>넘버포바버샵</t>
+          <t>오아이오헤어</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>no4barbershop@naver.com</t>
+          <t>sosim1203@naver.com</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>0507-1472-3437</t>
+          <t>0507-1376-5196</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로220길 20 2층</t>
+          <t>서울특별시 관악구 봉천로 369 2층 오아이오 미용실</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>http://instagram.com/no.4_barbershop</t>
+          <t>https://www.instagram.com/oio_hairshop?igsh=NTU3MnBieTQweDhs&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -13241,13 +13245,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>606</v>
+        <v>7742</v>
       </c>
       <c r="Q138" t="n">
-        <v>8</v>
+        <v>613</v>
       </c>
       <c r="R138" t="n">
-        <v>614</v>
+        <v>8355</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -13256,12 +13260,12 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>1047506236</t>
+          <t>1834113005</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1047506236</t>
+          <t>https://m.place.naver.com/place/1834113005</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
@@ -13273,34 +13277,34 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>리맨즈헤어 서울대입구역점</t>
+          <t>더숲헤어 봉천점</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>alroha57@naver.com</t>
+          <t>thesoophair1@naver.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0507-1467-1225</t>
+          <t>0507-1415-0817</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 봉천로 509 2층</t>
+          <t>서울특별시 관악구 남부순환로 1729 1층, 2층</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>http://instagram.com/remens_ohgun/</t>
+          <t>https://www.instagram.com/thesoophair</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -13335,13 +13339,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1860</v>
+        <v>6111</v>
       </c>
       <c r="Q139" t="n">
-        <v>156</v>
+        <v>347</v>
       </c>
       <c r="R139" t="n">
-        <v>2016</v>
+        <v>6458</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -13350,12 +13354,12 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>1129295904</t>
+          <t>1045756452</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129295904</t>
+          <t>https://m.place.naver.com/place/1045756452</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
@@ -13367,30 +13371,34 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>프랜차이즈본사</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>미창조</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>세빈헤어</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>suba67932@naver.com</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>02-588-1837</t>
+          <t>0507-1320-3186</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 2082-29 동일빌딩 5층</t>
+          <t>서울특별시 관악구 은천로 1 1층</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/mcmartmichangzo/products/11395491573</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -13400,7 +13408,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -13421,34 +13429,8680 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P140" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1</v>
+      </c>
+      <c r="R140" t="n">
+        <v>31</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>1849428474</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1849428474</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>얼번스트리트 헤어샵 포레스트점</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>bu03060@naver.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>cto@handsos.com</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0507-1494-1142</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1625 2층</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/13/bizes/225593</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>6438</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>1088</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7526</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>1823478174</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1823478174</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>아끌리오헤어</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>aclio7410@naver.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0507-1433-5272</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 쑥고개로 70 2층 스카이빌딩</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.cclio_official</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>664</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>25</v>
+      </c>
+      <c r="R142" t="n">
+        <v>689</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>1465124339</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1465124339</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>메타 맨즈헤어</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ramg91@naver.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0507-1406-7959</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로28길 4 1층 메타 맨즈헤어</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q143" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
+      <c r="R143" t="n">
+        <v>60</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>2064093017</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064093017</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>아빈헤어</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>avinhair@naver.com</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0507-1418-3350</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로 222 2층</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/avinhair</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>832</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>17</v>
+      </c>
+      <c r="R144" t="n">
+        <v>849</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>1668757757</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1668757757</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>이훈ALL30000 서울대입구역점</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>olivia0069@naver.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>02-872-8881</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 중앙길 5 2층 이훈헤어</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>15</v>
+      </c>
+      <c r="R145" t="n">
+        <v>625</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>38703998</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38703998</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>로이드밤 낙성대점</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>pinggr9920@naver.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0507-1369-4419</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1934 낙성대빌딩 3층 로이드밤 헤어</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pinggr9920</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>3391</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>231</v>
+      </c>
+      <c r="R146" t="n">
+        <v>3622</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>1656408992</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1656408992</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>살롱드키코 사당역점</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>todn0106@naver.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0507-1433-3008</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 2050</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/todn0106</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>3260</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>160</v>
+      </c>
+      <c r="R147" t="n">
+        <v>3420</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>1286273885</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1286273885</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>cafe de hair</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>sniper785@naver.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>02-588-7850</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 승방3길 1 1층 카페디헤어</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sniper785</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>1060</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>79</v>
+      </c>
+      <c r="R148" t="n">
+        <v>1139</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>33605859</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33605859</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>지안헤어</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>geeann8862@naver.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0507-1414-6288</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 법원단지길 46 1층</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/geeann8862</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>2</v>
+      </c>
+      <c r="R149" t="n">
+        <v>32</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>1868712205</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1868712205</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>베르디헤어 서울대입구역점</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>verdi_hair@naver.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0507-1401-9765</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로15길 24 1층</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>http://blog.naver.com/verdi_hair</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>493</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>69</v>
+      </c>
+      <c r="R150" t="n">
+        <v>562</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>38300119</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38300119</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>꾸찌헤어</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>02-885-4460</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 중앙길 7 꾸찌헤어</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>2</v>
+      </c>
+      <c r="R151" t="n">
+        <v>116</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>37049518</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37049518</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>어바웃9 신림역 헤어샵</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>puresummer@naver.com</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0507-1401-4999</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1597 3층</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/puresummer</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>4656</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>1100</v>
+      </c>
+      <c r="R152" t="n">
+        <v>5756</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>18733471</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18733471</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>블루클럽 사당점</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>alzzalsc@naver.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>jws0413@gamil.com</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>02-3471-0879</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 2062</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>http://www.blueclub.co.kr/</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>330</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>2</v>
+      </c>
+      <c r="R153" t="n">
+        <v>332</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>11729703</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11729703</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>까미헤어솔루션</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남현길 53</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>1</v>
+      </c>
+      <c r="R154" t="n">
+        <v>41</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>682463864</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/682463864</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>큐맨헤어 사당역점</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>qmanhair@naver.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0507-1473-7993</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 과천대로 947 4층</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/qmanhair_isu</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>1618</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>543</v>
+      </c>
+      <c r="R155" t="n">
+        <v>2161</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>1614846742</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614846742</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>박준뷰티랩 신림점</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ggyo1308@naver.com</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>0507-1417-2028</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1610 3층</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ggyo1308</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>24467</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>1859</v>
+      </c>
+      <c r="R156" t="n">
+        <v>26326</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>34087367</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34087367</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>헤이즈 헤어</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>power0942@naver.com</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0507-1317-6640</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림동5가길 17 1층 헤이즈헤어</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/d.tyyy/</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>1</v>
+      </c>
+      <c r="R157" t="n">
+        <v>161</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>1895495478</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1895495478</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>더모아헤어</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>jh-holicday@naver.com</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0507-1337-8440</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로 351 2층</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_moa__</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>4873</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>154</v>
+      </c>
+      <c r="R158" t="n">
+        <v>5027</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>1483519576</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1483519576</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>애즈온헤어</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>miraemiree@naver.com</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0507-1484-1465</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 과천대로 947 5층</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/miraemiree</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>1407</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>117</v>
+      </c>
+      <c r="R159" t="n">
+        <v>1524</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>1887750560</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1887750560</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>유포리아헤어 쟝피엘 낙성대역점</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>euphoria_sina@naver.com</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0507-1416-0898</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1915 2층 유포리아헤어 쟝피엘 낙성대역점</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/euphoria_sina</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>15858</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>1921</v>
+      </c>
+      <c r="R160" t="n">
+        <v>17779</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>21387752</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21387752</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>살롱드스누</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0507-1362-9227</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로 1 서울대학교 대학원생활관 900동</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>686</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>16</v>
+      </c>
+      <c r="R161" t="n">
+        <v>702</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>1304534143</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1304534143</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>지베르니헤어</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0507-1301-9264</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 호암로26길 64 2층</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>2</v>
+      </c>
+      <c r="R162" t="n">
+        <v>38</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>694389829</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/694389829</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>네추럴데이즈 낙성대본점</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0507-1342-2984</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1910 리더스빌 1층 네추럴데이즈 낙성대점</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>1996</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>129</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2125</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>36668140</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36668140</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>미와끼 헤어살롱</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>hjstylemm@naver.com</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>02-864-7831</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로 179-6 종현아트빌 101호 미와끼 헤어살롱</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>13</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>1387321668</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1387321668</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>가을헤어 사당역 본점</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ookk1254@naver.com</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0507-1330-2302</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 과천대로 949 가호 3층</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ookk1254</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>3480</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>49</v>
+      </c>
+      <c r="R165" t="n">
+        <v>3529</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>1558110094</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1558110094</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>선하다헤어</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>shimmin0115@naver.com</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>0507-1425-0481</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 청림길 5 1층</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>38</v>
+      </c>
+      <c r="R166" t="n">
+        <v>262</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>1126145782</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1126145782</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>젠틀맨</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>dannykim2010@naver.com</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>02-582-3352</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남현1길 2</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>http://gentlemangut.itrocks.kr/</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>1924371756</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1924371756</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>유트리헤어 구로디지털단지점</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>howareyousani@naver.com</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>0507-1389-9486</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 시흥대로 558-1 1동 3층 303호</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/utreehair</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>2261</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>330</v>
+      </c>
+      <c r="R168" t="n">
+        <v>2591</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>1883708609</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1883708609</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>박승철헤어스투디오 서울대입구역점</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>0507-1401-8787</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1820 에그옐로우 6층</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/psc_seoul</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>37854</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>1475</v>
+      </c>
+      <c r="R169" t="n">
+        <v>39329</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>154070837</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/154070837</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>준오헤어 신림역2호점</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>nice3006@naver.com</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>0507-1439-0608</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로 315 프레퍼스 3층 준오헤어</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://www.junohair.com/en/junohair/shop_info?idx=109</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>21377</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>2326</v>
+      </c>
+      <c r="R170" t="n">
+        <v>23703</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>35386890</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35386890</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>하미스토리</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>hami_story@naver.com</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0507-1400-1698</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1843 1층 건물뒷편 통유리 쪽으로 들어오시면 됩니다</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hami_story</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>609</v>
+      </c>
+      <c r="R171" t="n">
+        <v>674</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>31212768</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31212768</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>제오헤어 봉천점</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>selp2000@naver.com</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>02-888-0535</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1728 2층</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/selp2000</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>3758</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>426</v>
+      </c>
+      <c r="R172" t="n">
+        <v>4184</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>20481189</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20481189</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>살롱드르망 붙임머리 사당점</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>amanda231@naver.com</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0507-1330-0936</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 과천대로 939 르메이에르강남타운2 1층</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_BKXxhC</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>690</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>223</v>
+      </c>
+      <c r="R173" t="n">
+        <v>913</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>38705842</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38705842</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>준오헤어 낙성대역점</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>juno_nsd@naver.com</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0507-1485-0605</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1931 2층</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/juno_nsd</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>15193</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>887</v>
+      </c>
+      <c r="R174" t="n">
+        <v>16080</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>557191513</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/557191513</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>에이바헤어 서울대입구역점</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0507-1435-2310</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로 164 대우디오슈페리움 1단지 3층 311호</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://www.avahair.co.kr/</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>432</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>83</v>
+      </c>
+      <c r="R175" t="n">
+        <v>515</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>2039718265</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2039718265</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>신림붙임머리조조헤어</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>lhs3045@naver.com</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0507-1371-7252</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림동7길 51</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lhs3045</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>1084</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>142</v>
+      </c>
+      <c r="R176" t="n">
+        <v>1226</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>36620553</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36620553</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>헤어온유 신림역점</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>growing_harim@naver.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0507-1384-9818</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1588 2층 헤어온유 신림역점</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onyou_harim?igsh=MXN6Z25weXF4bjJvNw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>996</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>488</v>
+      </c>
+      <c r="R177" t="n">
+        <v>1484</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>2030885293</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2030885293</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>펫프렌즈애견미용실&amp;호텔</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>petfriends_@naver.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0507-1447-5549</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 법원단지21길 1 1층 펫프렌즈</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://link.groomernote.com/petfriends</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>24</v>
+      </c>
+      <c r="R178" t="n">
+        <v>116</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>1131877359</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1131877359</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>샴푸보이</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>tqncksqpdu49721@naver.com</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>02-582-3015</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남현길 55 1층 101호</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" t="n">
+        <v>2</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>380759917</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/380759917</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>더감동샵</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>070-4300-9926</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1541-1 1층</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>21</v>
+      </c>
+      <c r="R180" t="n">
+        <v>56</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>772391606</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/772391606</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>에이바헤어 신대방역점</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>jgh2543@naver.com</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0507-1328-2543</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신사로 102 2층</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jgh2543</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>3485</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>93</v>
+      </c>
+      <c r="R181" t="n">
+        <v>3578</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>1891967920</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1891967920</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>투헤어</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ojh3651@naver.com</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0507-1377-3650</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 쑥고개로 100</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ojh3651</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>52</v>
+      </c>
+      <c r="R182" t="n">
+        <v>262</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>31098531</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31098531</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>헤어수담 봉천역점</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>yhj3817@naver.com</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>0507-1472-8258</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 은천로 48 1층</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hair_soodam</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>2028</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>50</v>
+      </c>
+      <c r="R183" t="n">
+        <v>2078</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>1289218110</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1289218110</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>아바드헤어 사당역점</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>bellentae@naver.com</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0507-1380-7453</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 과천대로 939 르메이에르 강남타운2차 B1층 103-2호</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tae_eee__</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>20</v>
+      </c>
+      <c r="R184" t="n">
+        <v>65</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>2003793145</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2003793145</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>비앙뜨 살롱</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>viangttehair@naver.com</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>0507-1377-0529</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로72길 5 1층 비앙뜨살롱</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/viangttehair</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>1413</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>136</v>
+      </c>
+      <c r="R185" t="n">
+        <v>1549</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>1699126082</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1699126082</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>세연 헤어랜드</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남현4길 14 . 1층 101호 세연헤어랜드</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/seyeon_hairland</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="n">
+        <v>14</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>1096150756</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1096150756</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>오오디</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>vvv0031@naver.com</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0507-1495-0828</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로237길 3</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/___ood__</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>69</v>
+      </c>
+      <c r="R187" t="n">
+        <v>387</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>1037341527</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1037341527</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>살롱드오늘</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>0507-1355-1299</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로 387 1층</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>1</v>
+      </c>
+      <c r="R188" t="n">
+        <v>256</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>1701742522</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1701742522</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>에이점헤어 서울대입구점</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>0507-1372-9330</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1835-5 1층2층</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.hair_s</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>1775</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>291</v>
+      </c>
+      <c r="R189" t="n">
+        <v>2066</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>2074303770</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2074303770</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>호용희헤어 봉천점</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>aram0924@naver.com</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>0507-1371-5979</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1742-1 1층,2층</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>6</v>
+      </c>
+      <c r="R190" t="n">
+        <v>163</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>36561480</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36561480</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>고담맨즈헤어</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>llw7503@naver.com</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>0507-1484-5532</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로64길 17 한서빌딩 2층 고담맨즈헤어</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/godam___/</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>32761</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>268</v>
+      </c>
+      <c r="R191" t="n">
+        <v>33029</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>1042079600</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1042079600</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>마샬헤어샵</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>youjiin56@naver.com</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>02-3471-1769</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로262길 15 리베하우스</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
+        <v>1</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>20940621</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20940621</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>헤어 감동 그자체</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>mypjy9707@naver.com</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1929-9 2층</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mypjy9707</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>2577</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>248</v>
+      </c>
+      <c r="R193" t="n">
+        <v>2825</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>1767609827</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1767609827</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>오늘헤어</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>0507-1372-3667</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 호암로 585 102호</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>37</v>
+      </c>
+      <c r="R194" t="n">
+        <v>199</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>1856614677</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1856614677</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>바바헤어 서울대역점</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>hrpark9048@naver.com</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>02-877-9214</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로 201 3층</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baba_s2_eoul/</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>1919</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>13</v>
+      </c>
+      <c r="R195" t="n">
+        <v>1932</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>842792737</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/842792737</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>희쁨헤어</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>dmsid0721@naver.com</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>0507-1336-0232</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림동길 26 신림빌딩 2층 희쁨헤어</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dmsid0721</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>1257</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>292</v>
+      </c>
+      <c r="R196" t="n">
+        <v>1549</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>1323642385</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1323642385</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>어바웃9 서울대입구미용실</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>andoo7@naver.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>0507-1389-3009</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1827 2층</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>http://instagram.com/about9insun</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>3192</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>248</v>
+      </c>
+      <c r="R197" t="n">
+        <v>3440</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>1694153087</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1694153087</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>순수 서울대점</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>hairnono1@naver.com</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>0507-1343-6510</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로 198 2층</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hairnono1</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>2983</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>801</v>
+      </c>
+      <c r="R198" t="n">
+        <v>3784</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>32805932</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32805932</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>라포헤어</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>jinjakala@naver.com</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>0507-1315-3908</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 낙성대역길 32 1층</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rapport_cin/</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>47</v>
+      </c>
+      <c r="R199" t="n">
+        <v>225</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>18710295</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18710295</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>선화헤어살롱</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>gugabp8336@naver.com</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>0507-1392-5627</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 국회단지2길 31 1층</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/seonhwaheeosalrong</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>5</v>
+      </c>
+      <c r="R200" t="n">
+        <v>17</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>1881375347</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1881375347</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>리안헤어 봉천역점</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>wlduddk1220@naver.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>0507-1380-9966</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1739 지성빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wlduddk1220</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>4916</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>168</v>
+      </c>
+      <c r="R201" t="n">
+        <v>5084</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>645013168</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/645013168</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>까리아띠헤어</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>gkdbwjd0806@naver.com</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>0507-1382-0131</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 청룡1길 19 1층 4호</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
+        <v>95</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>1214830545</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1214830545</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>썬씨크</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>pakjjso@naver.com</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>0507-1329-3946</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로210길 35 101호 아트빌</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pakjjso</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>2</v>
+      </c>
+      <c r="R203" t="n">
+        <v>8</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>1897093080</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1897093080</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>미첼헤어</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>parkvely1228@naver.com</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>02-867-9859</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로 294 102호</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>1</v>
+      </c>
+      <c r="R204" t="n">
+        <v>13</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>1609201269</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1609201269</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>혜영머리방</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>02-521-6933</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남현3길 26</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
+        <v>17</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>1057154370</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057154370</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>데이벨 서울대입구역점</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>zo0eun@naver.com</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>0507-1410-0571</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1840 아데르 2층 R08호</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/youngs_st/</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>6</v>
+      </c>
+      <c r="R206" t="n">
+        <v>29</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>1093023282</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1093023282</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>하울붙임머리 신림점</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>lbl9887@naver.com</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>0507-1397-7497</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로188길 9 4층</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/howl_hair_</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>87</v>
+      </c>
+      <c r="R207" t="n">
+        <v>169</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>2018729246</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2018729246</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>김정숙헤어샵</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>02-522-8731</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 승방길 7</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>13</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>20879942</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20879942</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>이가자헤어비스 신림삼모타워점</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>sdoul@naver.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>0507-1334-8322</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신원로 35 삼모더프라임타워 2층</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>7252</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>359</v>
+      </c>
+      <c r="R209" t="n">
+        <v>7611</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>1287988275</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1287988275</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>로이드밤 신대방역점</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>0507-1464-1740</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로 360 2층 로이드밤 신대방역점</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lloydbomb6644</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>4232</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>27</v>
+      </c>
+      <c r="R210" t="n">
+        <v>4259</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>1121450152</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1121450152</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>보그헤어 신림점</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>epkcs_0112@naver.com</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>0507-1497-8086</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관천로 52 2층</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stylistsia</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>641</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>66</v>
+      </c>
+      <c r="R211" t="n">
+        <v>707</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>1021708153</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1021708153</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>아우라헤어</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로30길 11 1층 102호</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>1</v>
+      </c>
+      <c r="R212" t="n">
+        <v>4</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>2064903757</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064903757</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>헤어바이유</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>csgi0402@naver.com</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>0507-1398-8859</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 신림로11길 31 1층</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hair.byu</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>669</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>2</v>
+      </c>
+      <c r="R213" t="n">
+        <v>671</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>1580523134</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1580523134</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>헤어 라비에</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>coffee4life@naver.com</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>0507-1344-8348</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 1913 2층 헤어라비에</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>672</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>254</v>
+      </c>
+      <c r="R214" t="n">
+        <v>926</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>1543674696</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1543674696</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>유엔나헤어</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>youna_1025@naver.com</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>0507-1375-7882</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 중앙길 15-1 아티크빌딩 101호</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/youna_1025</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>466</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>31</v>
+      </c>
+      <c r="R215" t="n">
+        <v>497</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>1600376887</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1600376887</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>로위 사당역점</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>loweisu@naver.com</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>0507-1344-1111</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 과천대로 939 르메이에르타운 2차 4층 401호</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://https//www.lo-we.kr/</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>17</v>
+      </c>
+      <c r="R216" t="n">
+        <v>24</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>2064949611</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064949611</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>박승철헤어스투디오 서울대샤로수길점</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>d_andj@naver.com</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>0507-1478-8791</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로 168 대우디오슈페리움2단지 3층 307호</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/psc_sharosu</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>36584</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>1395</v>
+      </c>
+      <c r="R217" t="n">
+        <v>37979</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>1297643631</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1297643631</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>건물,구축물해체공사</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>철거천국 관악점</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>kang0825123@naver.com</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>0504-1360-1077</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 승방길 27 제 A동 제B102호-2026</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>72</v>
+      </c>
+      <c r="R218" t="n">
+        <v>72</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>2082818976</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2082818976</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>루이네</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>luinedesign@naver.com</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 구암길 37 1층 루이네(반려견미용실)</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/louis_petsalon</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>2</v>
+      </c>
+      <c r="R219" t="n">
+        <v>25</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>1801986146</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1801986146</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>힐링아로마 보그펫</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>vogue_pet@naver.com</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>0507-1330-2915</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 청림길 14 힐링아로마 보그펫</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/vogue_pet</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>100</v>
+      </c>
+      <c r="R220" t="n">
+        <v>146</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>1666008066</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1666008066</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>블링블링하개</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>0507-1319-2632</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 난곡로43길 8 1층 블링블링하개</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/it_s_bling_bling</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>11</v>
+      </c>
+      <c r="R221" t="n">
+        <v>92</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>1196739865</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1196739865</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>아우어썸머 바버샵</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>durudgh118@naver.com</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>0507-1489-2464</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 관악로10길 31-20 라온아뜨 1층 아우어썸머 바버샵</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/k_ho0602/</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>613</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>47</v>
+      </c>
+      <c r="R222" t="n">
+        <v>660</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>1677236508</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1677236508</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>애리조나</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>0507-1362-9905</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로200길 9 1층</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barber_kenzo</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>508</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>32</v>
+      </c>
+      <c r="R223" t="n">
+        <v>540</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>1074430929</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1074430929</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>인페르노바버샵</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>wnstjd7878@naver.com</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>0507-1319-6246</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 은천로 170 1층</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wnstjd7878</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>739</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>50</v>
+      </c>
+      <c r="R224" t="n">
+        <v>789</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>1853395879</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853395879</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>지금은나의이발사</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>mybaber@naver.com</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0505-300-8835</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 낙성대역길 39 1층</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mybaber</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>1</v>
+      </c>
+      <c r="R225" t="n">
+        <v>22</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>1856833468</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1856833468</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>페니레인바버샵</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>1024ty@naver.com</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>0507-1392-2465</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 조원중앙로2길 121 1층 바버샵</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/1024ty</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>2</v>
+      </c>
+      <c r="R226" t="n">
+        <v>118</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>1833183810</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1833183810</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>쎄 비 바버샵</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>barberblxk@naver.com</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>0507-1306-4820</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로214길 29 1층</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/c.est_b_barbershop.kr</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>496</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>79</v>
+      </c>
+      <c r="R227" t="n">
+        <v>575</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>1438442640</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1438442640</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>넘버포바버샵</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>no4barbershop@naver.com</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>0507-1472-3437</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로220길 20 2층</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>http://instagram.com/no.4_barbershop</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>606</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>8</v>
+      </c>
+      <c r="R228" t="n">
+        <v>614</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>1047506236</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1047506236</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>리맨즈헤어 서울대입구역점</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>alroha57@naver.com</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>0507-1467-1225</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 봉천로 509 2층</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>http://instagram.com/remens_ohgun/</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>1860</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>156</v>
+      </c>
+      <c r="R229" t="n">
+        <v>2016</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>1129295904</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1129295904</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>슈퍼맨즈</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>0507-1314-1893</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 양녕로 32-1 1층</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermans_bbs</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>3</v>
+      </c>
+      <c r="R230" t="n">
+        <v>60</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>1761026602</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1761026602</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>디그니티바버샵</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>hustlersbarbershop@naver.com</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 과천대로 949 4층</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/dignitybarber_official</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>3</v>
+      </c>
+      <c r="R231" t="n">
+        <v>231</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>1211924180</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1211924180</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>컴퓨터프로그래밍,정보서비스업</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>한국미용데이터</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>vukapro@naver.com</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>1566-5641</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 2072 2층</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@vukapro_official</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>0</v>
+      </c>
+      <c r="R232" t="n">
+        <v>8</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>36073166</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36073166</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>프랜차이즈본사</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>미창조</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>02-588-1837</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>서울특별시 관악구 남부순환로 2082-29 동일빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/mcmartmichangzo/products/11395491573</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="n">
         <v>218</v>
       </c>
-      <c r="R140" t="n">
+      <c r="R233" t="n">
         <v>218</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T140" t="inlineStr">
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
         <is>
           <t>11857938</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="U233" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/11857938</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr">
+      <c r="V233" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
